--- a/output/stock_quant_scores/GS_info.xlsx
+++ b/output/stock_quant_scores/GS_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ2"/>
+  <dimension ref="A1:FU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,235 +1056,255 @@
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1369,7 +1389,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. David M. Solomon', 'age': 62, 'title': 'Chairman &amp; CEO', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 11450298, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John E. Waldron', 'age': 54, 'title': 'President, COO &amp; Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 14464600, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kathryn H. Ruemmler', 'age': 52, 'title': 'Chief Legal Officer, Secretary &amp; General Counsel', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 9329689, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John F. W. Rogers', 'age': 67, 'title': 'Executive VP, Lead Director &amp; Secretary to the Board of Directors', 'yearBorn': 1957, 'fiscalYear': 2024, 'totalPay': 7490528, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. J. D. Gardner', 'title': 'Director', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sheara J. Fredman', 'age': 48, 'title': 'Controller &amp; Chief Accounting Officer', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Francois-Xavier  De Mallmann', 'title': 'Chair of Goldman Sachs EMEA &amp; Chair of Investment Banking.', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Marco  Argenti', 'title': 'Partner &amp; Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael J. Richman J.D.', 'title': 'Chief Compliance Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Sam  Morgan', 'title': 'Global Co-Head of client coverage for Global Banking &amp; Markets and Global Head of Sales', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. David M. Solomon', 'age': 62, 'title': 'Chairman &amp; CEO', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 11450298, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John E. Waldron', 'age': 54, 'title': 'President, COO &amp; Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 14464600, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Denis P. Coleman III', 'age': 50, 'title': 'Chief Financial Officer', 'yearBorn': 1974, 'fiscalYear': 2024, 'totalPay': 10435693, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kathryn H. Ruemmler', 'age': 52, 'title': 'Chief Legal Officer, Secretary &amp; General Counsel', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 9329689, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John F. W. Rogers', 'age': 67, 'title': 'Executive VP, Lead Director &amp; Secretary to the Board of Directors', 'yearBorn': 1957, 'fiscalYear': 2024, 'totalPay': 7490528, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. J. D. Gardner', 'title': 'Director', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sheara J. Fredman', 'age': 48, 'title': 'Controller &amp; Chief Accounting Officer', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Francois-Xavier  De Mallmann', 'title': 'Chair of Goldman Sachs EMEA &amp; Chair of Investment Banking.', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Marco  Argenti', 'title': 'Partner &amp; Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael J. Richman J.D.', 'title': 'Chief Compliance Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1405,34 +1425,34 @@
         <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>806.3200000000001</v>
+        <v>794.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>809.55</v>
+        <v>797.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>793.54</v>
+        <v>795.13</v>
       </c>
       <c r="AE2" t="n">
-        <v>812.8375</v>
+        <v>809.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>806.3200000000001</v>
+        <v>794.76</v>
       </c>
       <c r="AG2" t="n">
-        <v>809.55</v>
+        <v>797.16</v>
       </c>
       <c r="AH2" t="n">
-        <v>793.54</v>
+        <v>795.13</v>
       </c>
       <c r="AI2" t="n">
-        <v>812.8375</v>
+        <v>809.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AL2" t="n">
         <v>1756425600</v>
@@ -1447,31 +1467,31 @@
         <v>1.402</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.531277</v>
+        <v>17.66865</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19.151106</v>
+        <v>19.309673</v>
       </c>
       <c r="AR2" t="n">
-        <v>845214</v>
+        <v>1146879</v>
       </c>
       <c r="AS2" t="n">
-        <v>845214</v>
+        <v>1142034</v>
       </c>
       <c r="AT2" t="n">
-        <v>1973873</v>
+        <v>1912360</v>
       </c>
       <c r="AU2" t="n">
-        <v>1813930</v>
+        <v>1715910</v>
       </c>
       <c r="AV2" t="n">
-        <v>1813930</v>
+        <v>1715910</v>
       </c>
       <c r="AW2" t="n">
-        <v>797.13</v>
+        <v>799</v>
       </c>
       <c r="AX2" t="n">
-        <v>797.5599999999999</v>
+        <v>806.6799999999999</v>
       </c>
       <c r="AY2" t="n">
         <v>2</v>
@@ -1480,7 +1500,7 @@
         <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>240941760512</v>
+        <v>242936709120</v>
       </c>
       <c r="BB2" t="n">
         <v>439.38</v>
@@ -1495,19 +1515,19 @@
         <v>47.41</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.397229</v>
+        <v>4.433637</v>
       </c>
       <c r="BG2" t="n">
-        <v>741.1215999999999</v>
+        <v>746.5722</v>
       </c>
       <c r="BH2" t="n">
-        <v>632.48785</v>
+        <v>635.4604</v>
       </c>
       <c r="BI2" t="n">
         <v>12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.014882429</v>
+        <v>0.015098898</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
@@ -1518,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>19719485440</v>
+        <v>18513571840</v>
       </c>
       <c r="BN2" t="n">
         <v>0.28401</v>
@@ -1530,31 +1550,31 @@
         <v>302721092</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5653760</v>
+        <v>6035304</v>
       </c>
       <c r="BR2" t="n">
-        <v>5980943</v>
+        <v>5735421</v>
       </c>
       <c r="BS2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BT2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0187</v>
+        <v>0.0199</v>
       </c>
       <c r="BV2" t="n">
         <v>0.00569</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.74318004</v>
+        <v>0.7431</v>
       </c>
       <c r="BX2" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0188</v>
+        <v>0.02</v>
       </c>
       <c r="BZ2" t="n">
         <v>302720992</v>
@@ -1563,7 +1583,7 @@
         <v>344.057</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.3133376</v>
+        <v>2.3324914</v>
       </c>
       <c r="CC2" t="n">
         <v>1735603200</v>
@@ -1581,19 +1601,19 @@
         <v>14707000320</v>
       </c>
       <c r="CH2" t="n">
-        <v>45.4</v>
+        <v>45.42</v>
       </c>
       <c r="CI2" t="n">
         <v>41.56</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.36</v>
+        <v>0.338</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.6417315</v>
+        <v>0.62087214</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CM2" t="n">
         <v>4</v>
@@ -1607,7 +1627,7 @@
         </is>
       </c>
       <c r="CP2" t="n">
-        <v>795.92</v>
+        <v>802.51</v>
       </c>
       <c r="CQ2" t="n">
         <v>855</v>
@@ -1710,7 +1730,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>Nasdaq Real Time Price</t>
+          <t>Delayed Quote</t>
         </is>
       </c>
       <c r="DU2" t="b">
@@ -1723,172 +1743,184 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>1758931188</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>NYQ</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>finmb_398625</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.975137</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>802.51</v>
+      </c>
+      <c r="EI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>925824600000</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0.17943732</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>803.95</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1.4400024</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>795.13 - 809.5</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1912360</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0.82646</v>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>439.38 - 825.25</t>
+        </is>
+      </c>
+      <c r="EU2" t="n">
+        <v>-22.73999</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-0.027555274</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>62.087215</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1759104000</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1760445000</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1760445000</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1760445000</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1760448600</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1760448600</v>
+      </c>
+      <c r="FD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>46.28841</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>17.33717</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>55.937805</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>0.07492618</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>167.04962</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>0.26287967</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>2.6 - Hold</t>
+        </is>
+      </c>
+      <c r="FP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FQ2" t="inlineStr">
+        <is>
           <t>Goldman Sachs Group, Inc. (The)</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1758740014</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>54.7984</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.07393982</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>163.43213</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.25839567</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>2.6 - Hold</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-1.2898135</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-10.400024</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>793.54 - 812.8375</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>1973873</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>356.53998</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.81146157</v>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>439.38 - 825.25</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-29.330017</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-0.035540767</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>64.17315000000001</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1759104000</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1760448600</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1760448600</v>
-      </c>
-      <c r="EZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>46.29209</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>17.193434</v>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FF2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>925824600000</v>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>NYQ</t>
-        </is>
-      </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>finmb_398625</t>
-        </is>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="FL2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="FN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>795.92</v>
-      </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="FT2" t="inlineStr">
         <is>
           <t>The Goldman Sachs</t>
         </is>
       </c>
-      <c r="FQ2" t="n">
-        <v>3.0242</v>
+      <c r="FU2" t="n">
+        <v>3.007</v>
       </c>
     </row>
   </sheetData>
